--- a/ms_tables/tableS2_disparity_n4_E_small_fam.xlsx
+++ b/ms_tables/tableS2_disparity_n4_E_small_fam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomas/Documents/GitHub/GvsP/ms_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1608AAD-ACCD-A942-AB0D-19CAE0525A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC120811-9B6F-F74C-A9A2-2D6EB0790A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27320" yWindow="620" windowWidth="27320" windowHeight="19860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -854,19 +854,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>986913</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>193022</xdr:rowOff>
+      <xdr:colOff>953949</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E20024E3-D599-C648-A936-43EFFABC5ABF}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{864AEC41-A95D-F445-8CA3-97F0187C7219}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -874,7 +874,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4796913" y="193022"/>
+              <a:off x="4773020" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -940,7 +940,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -998,7 +998,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1012,13 +1012,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E20024E3-D599-C648-A936-43EFFABC5ABF}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{864AEC41-A95D-F445-8CA3-97F0187C7219}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1026,7 +1026,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4796913" y="193022"/>
+              <a:off x="4773020" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1065,37 +1065,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -1108,19 +1108,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>798955</xdr:colOff>
+      <xdr:colOff>771071</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>191062</xdr:rowOff>
+      <xdr:rowOff>199571</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="13" name="TextBox 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3331CB8-21FA-614D-BF0E-62CA05F543E7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21131314-856B-BE43-8545-5B16695C8657}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1128,7 +1128,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2709574" y="191062"/>
+              <a:off x="2685142" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1163,6 +1163,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1194,73 +1252,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="13" name="TextBox 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3331CB8-21FA-614D-BF0E-62CA05F543E7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21131314-856B-BE43-8545-5B16695C8657}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1268,7 +1274,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2709574" y="191062"/>
+              <a:off x="2685142" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1298,9 +1304,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -1309,25 +1345,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1338,19 +1356,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1019883</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>193645</xdr:rowOff>
+      <xdr:colOff>989459</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="14" name="TextBox 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B14BE81A-A912-DB46-82A9-8DDFFD4CC27E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F03719C4-D268-614E-A21F-66792E47658D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1358,7 +1376,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3750945" y="193645"/>
+              <a:off x="3729030" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1490,13 +1508,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="14" name="TextBox 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B14BE81A-A912-DB46-82A9-8DDFFD4CC27E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F03719C4-D268-614E-A21F-66792E47658D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1504,7 +1522,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3750945" y="193645"/>
+              <a:off x="3729030" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1586,19 +1604,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>966593</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>193022</xdr:rowOff>
+      <xdr:colOff>958303</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30148C24-E2C4-C34D-AC41-989D85A5E177}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D9AF323-8060-3446-A092-5D1D2A0EFF9E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1606,7 +1624,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8373053" y="193022"/>
+              <a:off x="8369660" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1672,7 +1690,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1730,7 +1748,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1744,13 +1762,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30148C24-E2C4-C34D-AC41-989D85A5E177}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D9AF323-8060-3446-A092-5D1D2A0EFF9E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1758,7 +1776,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8373053" y="193022"/>
+              <a:off x="8369660" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1797,37 +1815,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -1840,19 +1858,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1388235</xdr:colOff>
+      <xdr:colOff>1383211</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>191062</xdr:rowOff>
+      <xdr:rowOff>199571</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
+            <xdr:cNvPr id="16" name="TextBox 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72BD9FCE-3D89-2C42-9EF2-B7DD3D7E7575}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24B6EF78-BA80-944C-8A20-1C0031E9DE22}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1860,7 +1878,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6277173" y="191062"/>
+              <a:off x="6281782" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1895,6 +1913,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1926,73 +2002,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
+            <xdr:cNvPr id="16" name="TextBox 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72BD9FCE-3D89-2C42-9EF2-B7DD3D7E7575}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24B6EF78-BA80-944C-8A20-1C0031E9DE22}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2000,7 +2024,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6277173" y="191062"/>
+              <a:off x="6281782" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2030,9 +2054,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -2041,25 +2095,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2070,19 +2106,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>999563</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>193645</xdr:rowOff>
+      <xdr:colOff>993813</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
+            <xdr:cNvPr id="17" name="TextBox 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C9F800C-9CBF-1D4D-AC1C-EBDFDF0E8350}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9692916B-1A7A-0942-82A9-5EF8E02EB053}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2090,7 +2126,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7327085" y="193645"/>
+              <a:off x="7325670" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2222,13 +2258,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
+            <xdr:cNvPr id="17" name="TextBox 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C9F800C-9CBF-1D4D-AC1C-EBDFDF0E8350}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9692916B-1A7A-0942-82A9-5EF8E02EB053}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2236,7 +2272,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7327085" y="193645"/>
+              <a:off x="7325670" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2318,19 +2354,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>966593</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>193022</xdr:rowOff>
+      <xdr:colOff>958303</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04717EFF-F53A-5249-A570-96B890FE0AF3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80DA0D4F-1077-1F42-AFC4-240CF3183DA8}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2338,7 +2374,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11924558" y="193022"/>
+              <a:off x="11925660" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2404,7 +2440,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -2462,7 +2498,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -2476,13 +2512,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04717EFF-F53A-5249-A570-96B890FE0AF3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80DA0D4F-1077-1F42-AFC4-240CF3183DA8}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2490,7 +2526,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11924558" y="193022"/>
+              <a:off x="11925660" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2529,37 +2565,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -2572,19 +2608,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1367915</xdr:colOff>
+      <xdr:colOff>1355996</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>191062</xdr:rowOff>
+      <xdr:rowOff>199571</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
+            <xdr:cNvPr id="19" name="TextBox 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35BEB028-EF28-E14E-B0A3-A3DFB40F09E0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{923B4548-1DD2-3646-87B1-7A6E862D6337}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2592,7 +2628,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9842074" y="191062"/>
+              <a:off x="9837782" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2627,6 +2663,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2658,73 +2752,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
+            <xdr:cNvPr id="19" name="TextBox 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35BEB028-EF28-E14E-B0A3-A3DFB40F09E0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{923B4548-1DD2-3646-87B1-7A6E862D6337}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2732,7 +2774,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9842074" y="191062"/>
+              <a:off x="9837782" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2762,9 +2804,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -2773,25 +2845,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2802,19 +2856,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>999563</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>193645</xdr:rowOff>
+      <xdr:colOff>993813</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="TextBox 10">
+            <xdr:cNvPr id="20" name="TextBox 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FEEC42D-1E00-7D49-8C28-EE7B841E62A7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DDDB1BF-8DD8-764D-9EC4-9CD2566AEFFA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2822,7 +2876,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10878590" y="193645"/>
+              <a:off x="10881670" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2954,13 +3008,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="TextBox 10">
+            <xdr:cNvPr id="20" name="TextBox 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FEEC42D-1E00-7D49-8C28-EE7B841E62A7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DDDB1BF-8DD8-764D-9EC4-9CD2566AEFFA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2968,7 +3022,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10878590" y="193645"/>
+              <a:off x="10881670" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
